--- a/data publikasi new 1.xlsx
+++ b/data publikasi new 1.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\APLIKASI PYTHON STREAMLIT 2026\DATA PRODI S1 MATEMATIKA USU\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C7C03C97-93F7-4861-B918-C635F7B26B49}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B23A87A7-474B-40BA-8A5B-50EC45344973}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="315" uniqueCount="217">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="497" uniqueCount="337">
   <si>
     <t>Judul</t>
   </si>
@@ -573,9 +573,6 @@
     <t>Optimization of Vehicle Routing Problem in the Context of E-commerce Logistics Distribution</t>
   </si>
   <si>
-    <t>Saib Suwilo; Opim Salim Sitompul; Mardiningsih; Rezzy Eko Caraka; Yunho Kim; Maengseok Noh</t>
-  </si>
-  <si>
     <t>Engineering Letters</t>
   </si>
   <si>
@@ -676,6 +673,370 @@
   </si>
   <si>
     <t>10.1088/1742-6596/2157/1/012003</t>
+  </si>
+  <si>
+    <t>The Classification Model of Learners Based on Diagnostic Assessment Results in E-learning With Machine Learning</t>
+  </si>
+  <si>
+    <t>Mesra Betty Yel; Muhammad Zarlis; Saib Suwilo; Syahril Efendi; Poltak Sihombing</t>
+  </si>
+  <si>
+    <t>Muhammad Zarlis; Saib Suwilo; Syahril Efendi; Poltak Sihombing</t>
+  </si>
+  <si>
+    <t>2022 1st International Conference on Software Engineering and Information Technology, ICoSEIT 2022</t>
+  </si>
+  <si>
+    <t>978-1-6654-7303-3</t>
+  </si>
+  <si>
+    <t>https://www.scopus.com/pages/publications/85148236539?origin=resultslist</t>
+  </si>
+  <si>
+    <t>https://ieeexplore.ieee.org/document/10030060</t>
+  </si>
+  <si>
+    <t>10.1109/ICoSEIT55604.2022</t>
+  </si>
+  <si>
+    <t>Performance Improvement of Grid Mapping K-Means with the Average Value at Grid Point</t>
+  </si>
+  <si>
+    <t>Salomo Ginting; Syahril Efendi; Saib Suwilo</t>
+  </si>
+  <si>
+    <t>Syahril Efendi; Saib Suwilo</t>
+  </si>
+  <si>
+    <t>IOP Conference Series: Earth and Environmental Science</t>
+  </si>
+  <si>
+    <t>https://www.scopus.com/pages/publications/85140245878?origin=resultslist</t>
+  </si>
+  <si>
+    <t>https://iopscience.iop.org/article/10.1088/1755-1315/1083/1/012082</t>
+  </si>
+  <si>
+    <t>https://www.scimagojr.com/journalsearch.php?q=19900195068&amp;tip=sid&amp;clean=0</t>
+  </si>
+  <si>
+    <t>10.1088/1755-1315/1083/1/012082</t>
+  </si>
+  <si>
+    <t>A COMBINATION K-MEANS CLUSTERING AND 2-OPT ALGORITHM FOR SOLVING THE TWO ECHELON E-COMMERCE LOGISTIC DISTRIBUTION</t>
+  </si>
+  <si>
+    <t>1734459X</t>
+  </si>
+  <si>
+    <t>Logforum</t>
+  </si>
+  <si>
+    <t>213-225</t>
+  </si>
+  <si>
+    <t>https://www.scopus.com/pages/publications/85138287885?origin=resultslist</t>
+  </si>
+  <si>
+    <t>https://www.logforum.net/volume18/issue2/abstract-6.html</t>
+  </si>
+  <si>
+    <t>https://www.scimagojr.com/journalsearch.php?q=21100913325&amp;tip=sid&amp;clean=0</t>
+  </si>
+  <si>
+    <t>10.17270/J.LOG.2022.734</t>
+  </si>
+  <si>
+    <t>The Mamdani Fuzzy Logic Engineering Analysis for Determining Weather Forecast</t>
+  </si>
+  <si>
+    <t>Aris Munandar Harahap; Saib Suwilo; Rahmat Widia Sembiring</t>
+  </si>
+  <si>
+    <t>Saib Suwilo</t>
+  </si>
+  <si>
+    <t>https://www.scopus.com/pages/publications/85102361490?origin=resultslist</t>
+  </si>
+  <si>
+    <t>https://iopscience.iop.org/article/10.1088/1742-6596/1783/1/012039</t>
+  </si>
+  <si>
+    <t>10.1088/1742-6596/1783/1/012039</t>
+  </si>
+  <si>
+    <t>Analysis of KNN in Classification of Firearms Sounds using Fast Fourier Transform</t>
+  </si>
+  <si>
+    <t>Muhammad Ari Afriansyah; Opim Salim Sitompul; Saib Suwilo</t>
+  </si>
+  <si>
+    <t>Opim Salim Sitompul; Saib Suwilo</t>
+  </si>
+  <si>
+    <t>Proceedings - 2021 4th International Conference on Computer and Informatics Engineering: IT-Based Digital Industrial Innovation for the Welfare of Society, IC2IE 2021</t>
+  </si>
+  <si>
+    <t>978-1-6654-4288-6</t>
+  </si>
+  <si>
+    <t>https://www.scopus.com/pages/publications/85124318828?origin=resultslist</t>
+  </si>
+  <si>
+    <t>https://ieeexplore.ieee.org/document/9649269</t>
+  </si>
+  <si>
+    <t>10.1109/IC2IE53219.2021.9649269</t>
+  </si>
+  <si>
+    <t>Additively weighted Hamming index of graphs</t>
+  </si>
+  <si>
+    <t>Mardiningsih; Saib Suwilo</t>
+  </si>
+  <si>
+    <t>https://www.scopus.com/pages/publications/85087786959?origin=resultslist</t>
+  </si>
+  <si>
+    <t>https://iopscience.iop.org/article/10.1088/1742-6596/1566/1/012028</t>
+  </si>
+  <si>
+    <t>10.1088/1742-6596/1566/1/012028</t>
+  </si>
+  <si>
+    <t>Community empowerment in improving the quality of regional potential for the tourism sector in North Sumatra</t>
+  </si>
+  <si>
+    <t>Elvina Herawati; Rosdanelli Hasibuan; Tulus</t>
+  </si>
+  <si>
+    <t>Book</t>
+  </si>
+  <si>
+    <t>Natural Resources, Environment, and Food and Energy Security Updates in North Sumatra</t>
+  </si>
+  <si>
+    <t>979-8-89530-283-5</t>
+  </si>
+  <si>
+    <t>https://www.scopus.com/pages/publications/105002205014?origin=resultslist</t>
+  </si>
+  <si>
+    <t>https://novapublishers.com/shop/natural-resources-environment-and-food-and-energy-security-updates-in-north-sumatra/</t>
+  </si>
+  <si>
+    <t>https://doi.org/10.52305/JPRQ7444</t>
+  </si>
+  <si>
+    <t>New class of n-order fractional differential equations and solvability in the double sequence space m2(∆uv, φ, p)</t>
+  </si>
+  <si>
+    <t>Hojjatollah Amiri Kayvanloo; Elvina Herawati; Mohammad Mursaleen</t>
+  </si>
+  <si>
+    <t>Elvina Herawati</t>
+  </si>
+  <si>
+    <t>Carpathian Journal of Mathematics</t>
+  </si>
+  <si>
+    <t>157-169</t>
+  </si>
+  <si>
+    <t>https://www.scopus.com/pages/publications/85208558042?origin=resultslist</t>
+  </si>
+  <si>
+    <t>https://www.carpathian.cunbm.utcluj.ro/wp-content/uploads/carpathian_2025_41_1_157_169.pdf</t>
+  </si>
+  <si>
+    <t>https://www.scimagojr.com/journalsearch.php?q=19700175588&amp;tip=sid&amp;clean=0</t>
+  </si>
+  <si>
+    <t>10.37193/CJM.2025.01.11</t>
+  </si>
+  <si>
+    <t>A Model for Multi-Period Facility-Location and Vehicle Assignment in Post-Disaster Areas under Uncertainty Using a Deep Learning Approach</t>
+  </si>
+  <si>
+    <t>Rizki Habibi; Herman Mawengkang; Tulus; Elvina Herawati</t>
+  </si>
+  <si>
+    <t>Herman Mawengkang; Tulus; Elvina Herawati</t>
+  </si>
+  <si>
+    <t>ICAISD 2025 - 2025 International Conference on Advanced Information Scientific Development: Artificial Intelligence: Advancing Research and Computational Innovations for Global Welfare, Proceedings</t>
+  </si>
+  <si>
+    <t>979-8-3315-7499-4</t>
+  </si>
+  <si>
+    <t>10.1109/ICAISD68166.2025.11385508</t>
+  </si>
+  <si>
+    <t>https://www.scopus.com/pages/publications/105035206522?origin=resultslist</t>
+  </si>
+  <si>
+    <t>https://ieeexplore.ieee.org/document/11385508</t>
+  </si>
+  <si>
+    <t>Simulation of pyrolysis process for waste plastics using Aspen Plus: Performance and emission analysis of PPO-diesel and PPO-biodiesel blends</t>
+  </si>
+  <si>
+    <t>Ilmi; Suherman; Suprianto; Syukril Hanif; Royhan Nahdi; Walid Ulfa Nasution; Muhammad Turmuzi; Arlina Nurbaity Lubis; Elvina Herawati; Tengku Silvana sinar</t>
+  </si>
+  <si>
+    <t>Muhammad Turmuzi; Arlina Nurbaity Lubis; Elvina Herawati; Tengku Silvana sinar</t>
+  </si>
+  <si>
+    <t>Case Studies in Thermal Engineering</t>
+  </si>
+  <si>
+    <t>2214157X</t>
+  </si>
+  <si>
+    <t>https://www.scopus.com/pages/publications/85209071709?origin=resultslist</t>
+  </si>
+  <si>
+    <t>https://www.sciencedirect.com/science/article/pii/S2214157X2401462X?via%3Dihub</t>
+  </si>
+  <si>
+    <t>1-23</t>
+  </si>
+  <si>
+    <t>https://www.scimagojr.com/journalsearch.php?q=21100262580&amp;tip=sid&amp;clean=0</t>
+  </si>
+  <si>
+    <t>10.1016/j.csite.2024.105431</t>
+  </si>
+  <si>
+    <t>On some geometric properties of sequence spaces of generalized arithmetic divisor sum function</t>
+  </si>
+  <si>
+    <t>Mohammad Mursaleen; Elvina Herawati</t>
+  </si>
+  <si>
+    <t>Journal of Inequalities and Applications</t>
+  </si>
+  <si>
+    <t>1-10</t>
+  </si>
+  <si>
+    <t>https://www.scopus.com/pages/publications/85205672197?origin=resultslist</t>
+  </si>
+  <si>
+    <t>https://link.springer.com/article/10.1186/s13660-024-03208-z</t>
+  </si>
+  <si>
+    <t>https://www.scimagojr.com/journalsearch.php?q=61774&amp;tip=sid&amp;clean=0</t>
+  </si>
+  <si>
+    <t>10.1186/s13660-024-03208-z</t>
+  </si>
+  <si>
+    <t>Fixed point theorems of Riesz-valued control function f in vector metric spaces</t>
+  </si>
+  <si>
+    <t>F. Fevin; Elvina Herawati</t>
+  </si>
+  <si>
+    <t>0094243X</t>
+  </si>
+  <si>
+    <t>https://www.scopus.com/pages/publications/85201234255?origin=resultslist</t>
+  </si>
+  <si>
+    <t>https://pubs.aip.org/aip/acp/article-abstract/3029/1/040008/3306387/Fixed-point-theorems-of-Riesz-valued-control?redirectedFrom=fulltext</t>
+  </si>
+  <si>
+    <t>10.1063/5.0192044</t>
+  </si>
+  <si>
+    <t>Combination of penalty function and gradient projection method in relaxed MIQQP-convex</t>
+  </si>
+  <si>
+    <t>Lasker P. Sinaga; Tulus; Elvina Herawati; Sawaluddin</t>
+  </si>
+  <si>
+    <t>Tulus; Elvina Herawati; Sawaluddin</t>
+  </si>
+  <si>
+    <t>https://www.scopus.com/pages/publications/85201225449?origin=resultslist</t>
+  </si>
+  <si>
+    <t>https://pubs.aip.org/aip/acp/article-abstract/3029/1/060007/3306416/Combination-of-penalty-function-and-gradient?redirectedFrom=fulltext</t>
+  </si>
+  <si>
+    <t>10.1063/5.0191793</t>
+  </si>
+  <si>
+    <t>The ? -Fatau property of lattice-normed vector lattices</t>
+  </si>
+  <si>
+    <t>Elvina Herawati; Erwin; Sawaluddin</t>
+  </si>
+  <si>
+    <t>https://www.scopus.com/pages/publications/85201200279?origin=resultslist</t>
+  </si>
+  <si>
+    <t>https://pubs.aip.org/aip/acp/article-abstract/3029/1/040007/3306386/The-Fatau-property-of-lattice-normed-vector?redirectedFrom=fulltext</t>
+  </si>
+  <si>
+    <t>10.1063/5.0191949</t>
+  </si>
+  <si>
+    <t>Constrained multiobjective optimization modeling of industrial waste transport travel routes using Pareto Frontier optimal decision model</t>
+  </si>
+  <si>
+    <t>Annisa Pratiwi; Mahyuddin Nasution; Elvina Herawati</t>
+  </si>
+  <si>
+    <t>Mahyuddin Nasution; Elvina Herawati</t>
+  </si>
+  <si>
+    <t>https://www.scopus.com/pages/publications/85201194474?origin=resultslist</t>
+  </si>
+  <si>
+    <t>https://pubs.aip.org/aip/acp/article-abstract/3029/1/060001/3306410/Constrained-multiobjective-optimization-modeling?redirectedFrom=fulltext</t>
+  </si>
+  <si>
+    <t>10.1063/5.0192313</t>
+  </si>
+  <si>
+    <t>Monte Carlo's simulation method from the law of large numbers on Chebyshev's inequality</t>
+  </si>
+  <si>
+    <t>Rifky Pradana Daulay; Open Darnius; Elvina Herawati</t>
+  </si>
+  <si>
+    <t>Open Darnius; Elvina Herawati</t>
+  </si>
+  <si>
+    <t>https://www.scopus.com/pages/publications/85160220673?origin=resultslist</t>
+  </si>
+  <si>
+    <t>https://pubs.aip.org/aip/acp/article-abstract/2714/1/020055/2889744/Monte-Carlo-s-simulation-method-from-the-law-of?redirectedFrom=fulltext</t>
+  </si>
+  <si>
+    <t>10.1063/5.0146688</t>
+  </si>
+  <si>
+    <t>Semantic Information Retrieval Models</t>
+  </si>
+  <si>
+    <t>Mahyuddin K.M. Nasution; Elvina Herawati; Marischa Elveny</t>
+  </si>
+  <si>
+    <t xml:space="preserve">
+Data Science with Semantic Technologies</t>
+  </si>
+  <si>
+    <t>10.1201/9781003310792-4</t>
+  </si>
+  <si>
+    <t>https://www.scopus.com/pages/publications/85160167751?origin=resultslist</t>
+  </si>
+  <si>
+    <t>https://www.taylorfrancis.com/chapters/edit/10.1201/9781003310792-4/semantic-information-retrieval-models-mahyuddin-nasution-elvina-herawati-marischa-elveny</t>
   </si>
 </sst>
 </file>
@@ -1012,7 +1373,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:R28"/>
+  <dimension ref="A1:R45"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="67.5703125" style="1" customWidth="1"/>
@@ -2075,16 +2436,16 @@
         <v>180</v>
       </c>
       <c r="C24" s="1" t="s">
-        <v>182</v>
+        <v>87</v>
       </c>
       <c r="D24" s="1" t="s">
         <v>2</v>
       </c>
       <c r="E24" s="1" t="s">
+        <v>182</v>
+      </c>
+      <c r="F24" s="1" t="s">
         <v>183</v>
-      </c>
-      <c r="F24" s="1" t="s">
-        <v>184</v>
       </c>
       <c r="G24" s="1">
         <v>2023</v>
@@ -2096,16 +2457,16 @@
         <v>1</v>
       </c>
       <c r="J24" s="3" t="s">
+        <v>184</v>
+      </c>
+      <c r="K24" s="2" t="s">
         <v>185</v>
       </c>
-      <c r="K24" s="2" t="s">
+      <c r="L24" s="2" t="s">
         <v>186</v>
       </c>
-      <c r="L24" s="2" t="s">
+      <c r="N24" s="2" t="s">
         <v>187</v>
-      </c>
-      <c r="N24" s="2" t="s">
-        <v>188</v>
       </c>
       <c r="P24" s="1">
         <v>7</v>
@@ -2116,7 +2477,7 @@
     </row>
     <row r="25" spans="1:18" ht="30" x14ac:dyDescent="0.25">
       <c r="A25" s="1" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="B25" s="1" t="s">
         <v>147</v>
@@ -2128,7 +2489,7 @@
         <v>31</v>
       </c>
       <c r="E25" s="1" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="F25" s="1">
         <v>17426588</v>
@@ -2143,19 +2504,19 @@
         <v>1</v>
       </c>
       <c r="J25" s="3" t="s">
+        <v>190</v>
+      </c>
+      <c r="K25" s="2" t="s">
         <v>191</v>
       </c>
-      <c r="K25" s="2" t="s">
+      <c r="L25" s="2" t="s">
         <v>192</v>
       </c>
-      <c r="L25" s="2" t="s">
+      <c r="N25" s="2" t="s">
         <v>193</v>
       </c>
-      <c r="N25" s="2" t="s">
+      <c r="O25" s="1" t="s">
         <v>194</v>
-      </c>
-      <c r="O25" s="1" t="s">
-        <v>195</v>
       </c>
       <c r="P25" s="1">
         <v>1</v>
@@ -2166,19 +2527,19 @@
     </row>
     <row r="26" spans="1:18" ht="30" x14ac:dyDescent="0.25">
       <c r="A26" s="1" t="s">
+        <v>195</v>
+      </c>
+      <c r="B26" s="1" t="s">
         <v>196</v>
       </c>
-      <c r="B26" s="1" t="s">
+      <c r="C26" s="1" t="s">
         <v>197</v>
-      </c>
-      <c r="C26" s="1" t="s">
-        <v>198</v>
       </c>
       <c r="D26" s="1" t="s">
         <v>31</v>
       </c>
       <c r="E26" s="1" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="F26" s="1">
         <v>17426588</v>
@@ -2193,19 +2554,19 @@
         <v>1</v>
       </c>
       <c r="J26" s="3" t="s">
+        <v>198</v>
+      </c>
+      <c r="K26" s="2" t="s">
         <v>199</v>
       </c>
-      <c r="K26" s="2" t="s">
+      <c r="L26" s="2" t="s">
         <v>200</v>
       </c>
-      <c r="L26" s="2" t="s">
+      <c r="N26" s="2" t="s">
+        <v>193</v>
+      </c>
+      <c r="O26" s="1" t="s">
         <v>201</v>
-      </c>
-      <c r="N26" s="2" t="s">
-        <v>194</v>
-      </c>
-      <c r="O26" s="1" t="s">
-        <v>202</v>
       </c>
       <c r="R26" s="1" t="s">
         <v>66</v>
@@ -2213,7 +2574,7 @@
     </row>
     <row r="27" spans="1:18" ht="30" x14ac:dyDescent="0.25">
       <c r="A27" s="1" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="B27" s="1" t="s">
         <v>147</v>
@@ -2225,7 +2586,7 @@
         <v>2</v>
       </c>
       <c r="E27" s="1" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="F27" s="1">
         <v>20893191</v>
@@ -2240,19 +2601,19 @@
         <v>1</v>
       </c>
       <c r="J27" s="3" t="s">
+        <v>204</v>
+      </c>
+      <c r="K27" s="2" t="s">
         <v>205</v>
       </c>
-      <c r="K27" s="2" t="s">
+      <c r="L27" s="2" t="s">
         <v>206</v>
       </c>
-      <c r="L27" s="2" t="s">
+      <c r="N27" s="2" t="s">
         <v>207</v>
       </c>
-      <c r="N27" s="2" t="s">
+      <c r="O27" s="1" t="s">
         <v>208</v>
-      </c>
-      <c r="O27" s="1" t="s">
-        <v>209</v>
       </c>
       <c r="R27" s="1" t="s">
         <v>66</v>
@@ -2260,19 +2621,19 @@
     </row>
     <row r="28" spans="1:18" ht="30" x14ac:dyDescent="0.25">
       <c r="A28" s="1" t="s">
+        <v>209</v>
+      </c>
+      <c r="B28" s="1" t="s">
         <v>210</v>
       </c>
-      <c r="B28" s="1" t="s">
+      <c r="C28" s="1" t="s">
         <v>211</v>
-      </c>
-      <c r="C28" s="1" t="s">
-        <v>212</v>
       </c>
       <c r="D28" s="1" t="s">
         <v>31</v>
       </c>
       <c r="E28" s="1" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="F28" s="1">
         <v>17426588</v>
@@ -2287,24 +2648,766 @@
         <v>1</v>
       </c>
       <c r="J28" s="3" t="s">
+        <v>212</v>
+      </c>
+      <c r="K28" s="2" t="s">
         <v>213</v>
       </c>
-      <c r="K28" s="2" t="s">
+      <c r="L28" s="2" t="s">
         <v>214</v>
       </c>
-      <c r="L28" s="2" t="s">
+      <c r="N28" s="2" t="s">
+        <v>193</v>
+      </c>
+      <c r="O28" s="1" t="s">
         <v>215</v>
-      </c>
-      <c r="N28" s="2" t="s">
-        <v>194</v>
-      </c>
-      <c r="O28" s="1" t="s">
-        <v>216</v>
       </c>
       <c r="P28" s="1">
         <v>6</v>
       </c>
       <c r="R28" s="1" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="29" spans="1:18" ht="45" x14ac:dyDescent="0.25">
+      <c r="A29" s="1" t="s">
+        <v>216</v>
+      </c>
+      <c r="B29" s="1" t="s">
+        <v>217</v>
+      </c>
+      <c r="C29" s="1" t="s">
+        <v>218</v>
+      </c>
+      <c r="D29" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="E29" s="1" t="s">
+        <v>219</v>
+      </c>
+      <c r="F29" s="1" t="s">
+        <v>220</v>
+      </c>
+      <c r="G29" s="1">
+        <v>2022</v>
+      </c>
+      <c r="K29" s="2" t="s">
+        <v>221</v>
+      </c>
+      <c r="L29" s="2" t="s">
+        <v>222</v>
+      </c>
+      <c r="O29" s="1" t="s">
+        <v>223</v>
+      </c>
+      <c r="P29" s="1">
+        <v>1</v>
+      </c>
+      <c r="R29" s="1" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="30" spans="1:18" ht="30" x14ac:dyDescent="0.25">
+      <c r="A30" s="1" t="s">
+        <v>224</v>
+      </c>
+      <c r="B30" s="1" t="s">
+        <v>225</v>
+      </c>
+      <c r="C30" s="1" t="s">
+        <v>226</v>
+      </c>
+      <c r="D30" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="E30" s="1" t="s">
+        <v>227</v>
+      </c>
+      <c r="F30" s="1">
+        <v>17551307</v>
+      </c>
+      <c r="G30" s="1">
+        <v>2022</v>
+      </c>
+      <c r="H30" s="1">
+        <v>1083</v>
+      </c>
+      <c r="I30" s="1">
+        <v>1</v>
+      </c>
+      <c r="K30" s="2" t="s">
+        <v>228</v>
+      </c>
+      <c r="L30" s="2" t="s">
+        <v>229</v>
+      </c>
+      <c r="N30" s="2" t="s">
+        <v>230</v>
+      </c>
+      <c r="O30" s="1" t="s">
+        <v>231</v>
+      </c>
+      <c r="R30" s="1" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="31" spans="1:18" ht="30" x14ac:dyDescent="0.25">
+      <c r="A31" s="1" t="s">
+        <v>232</v>
+      </c>
+      <c r="B31" s="1" t="s">
+        <v>86</v>
+      </c>
+      <c r="C31" s="1" t="s">
+        <v>87</v>
+      </c>
+      <c r="D31" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="E31" s="1" t="s">
+        <v>234</v>
+      </c>
+      <c r="F31" s="1" t="s">
+        <v>233</v>
+      </c>
+      <c r="G31" s="1">
+        <v>2022</v>
+      </c>
+      <c r="H31" s="1">
+        <v>18</v>
+      </c>
+      <c r="I31" s="1">
+        <v>2</v>
+      </c>
+      <c r="J31" s="3" t="s">
+        <v>235</v>
+      </c>
+      <c r="K31" s="2" t="s">
+        <v>236</v>
+      </c>
+      <c r="L31" s="2" t="s">
+        <v>237</v>
+      </c>
+      <c r="N31" s="2" t="s">
+        <v>238</v>
+      </c>
+      <c r="O31" s="1" t="s">
+        <v>239</v>
+      </c>
+      <c r="P31" s="1">
+        <v>10</v>
+      </c>
+      <c r="R31" s="1" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="32" spans="1:18" ht="30" x14ac:dyDescent="0.25">
+      <c r="A32" s="1" t="s">
+        <v>240</v>
+      </c>
+      <c r="B32" s="1" t="s">
+        <v>241</v>
+      </c>
+      <c r="C32" s="1" t="s">
+        <v>242</v>
+      </c>
+      <c r="D32" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="E32" s="1" t="s">
+        <v>189</v>
+      </c>
+      <c r="F32" s="1">
+        <v>17426588</v>
+      </c>
+      <c r="G32" s="1">
+        <v>2021</v>
+      </c>
+      <c r="H32" s="1">
+        <v>1873</v>
+      </c>
+      <c r="I32" s="1">
+        <v>1</v>
+      </c>
+      <c r="J32" s="3" t="s">
+        <v>198</v>
+      </c>
+      <c r="K32" s="2" t="s">
+        <v>243</v>
+      </c>
+      <c r="L32" s="2" t="s">
+        <v>244</v>
+      </c>
+      <c r="N32" s="2" t="s">
+        <v>193</v>
+      </c>
+      <c r="O32" s="1" t="s">
+        <v>245</v>
+      </c>
+      <c r="P32" s="1">
+        <v>1</v>
+      </c>
+      <c r="R32" s="1" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="33" spans="1:18" ht="75" x14ac:dyDescent="0.25">
+      <c r="A33" s="1" t="s">
+        <v>246</v>
+      </c>
+      <c r="B33" s="1" t="s">
+        <v>247</v>
+      </c>
+      <c r="C33" s="1" t="s">
+        <v>248</v>
+      </c>
+      <c r="D33" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="E33" s="1" t="s">
+        <v>249</v>
+      </c>
+      <c r="F33" s="1" t="s">
+        <v>250</v>
+      </c>
+      <c r="G33" s="1">
+        <v>2021</v>
+      </c>
+      <c r="K33" s="2" t="s">
+        <v>251</v>
+      </c>
+      <c r="L33" s="2" t="s">
+        <v>252</v>
+      </c>
+      <c r="O33" s="1" t="s">
+        <v>253</v>
+      </c>
+      <c r="R33" s="1" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="34" spans="1:18" ht="30" x14ac:dyDescent="0.25">
+      <c r="A34" s="1" t="s">
+        <v>254</v>
+      </c>
+      <c r="B34" s="1" t="s">
+        <v>255</v>
+      </c>
+      <c r="C34" s="1" t="s">
+        <v>255</v>
+      </c>
+      <c r="D34" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="E34" s="1" t="s">
+        <v>189</v>
+      </c>
+      <c r="F34" s="1">
+        <v>17426588</v>
+      </c>
+      <c r="G34" s="1">
+        <v>2021</v>
+      </c>
+      <c r="H34" s="1">
+        <v>1566</v>
+      </c>
+      <c r="I34" s="1">
+        <v>1</v>
+      </c>
+      <c r="J34" s="3" t="s">
+        <v>184</v>
+      </c>
+      <c r="K34" s="2" t="s">
+        <v>256</v>
+      </c>
+      <c r="L34" s="2" t="s">
+        <v>257</v>
+      </c>
+      <c r="N34" s="2" t="s">
+        <v>193</v>
+      </c>
+      <c r="O34" s="1" t="s">
+        <v>258</v>
+      </c>
+      <c r="R34" s="1" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="35" spans="1:18" ht="30" x14ac:dyDescent="0.25">
+      <c r="A35" s="1" t="s">
+        <v>259</v>
+      </c>
+      <c r="B35" s="1" t="s">
+        <v>260</v>
+      </c>
+      <c r="C35" s="1" t="s">
+        <v>260</v>
+      </c>
+      <c r="D35" s="1" t="s">
+        <v>261</v>
+      </c>
+      <c r="E35" s="1" t="s">
+        <v>262</v>
+      </c>
+      <c r="F35" s="1" t="s">
+        <v>263</v>
+      </c>
+      <c r="G35" s="1">
+        <v>2025</v>
+      </c>
+      <c r="K35" s="2" t="s">
+        <v>264</v>
+      </c>
+      <c r="L35" s="2" t="s">
+        <v>265</v>
+      </c>
+      <c r="O35" s="2" t="s">
+        <v>266</v>
+      </c>
+      <c r="R35" s="1" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="36" spans="1:18" ht="30" x14ac:dyDescent="0.25">
+      <c r="A36" s="1" t="s">
+        <v>267</v>
+      </c>
+      <c r="B36" s="1" t="s">
+        <v>268</v>
+      </c>
+      <c r="C36" s="1" t="s">
+        <v>269</v>
+      </c>
+      <c r="D36" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="E36" s="1" t="s">
+        <v>270</v>
+      </c>
+      <c r="F36" s="1">
+        <v>15842851</v>
+      </c>
+      <c r="G36" s="1">
+        <v>2025</v>
+      </c>
+      <c r="H36" s="1">
+        <v>41</v>
+      </c>
+      <c r="I36" s="1">
+        <v>1</v>
+      </c>
+      <c r="J36" s="3" t="s">
+        <v>271</v>
+      </c>
+      <c r="K36" s="2" t="s">
+        <v>272</v>
+      </c>
+      <c r="L36" s="2" t="s">
+        <v>273</v>
+      </c>
+      <c r="N36" s="2" t="s">
+        <v>274</v>
+      </c>
+      <c r="O36" s="1" t="s">
+        <v>275</v>
+      </c>
+      <c r="P36" s="1">
+        <v>5</v>
+      </c>
+      <c r="R36" s="1" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="37" spans="1:18" ht="75" x14ac:dyDescent="0.25">
+      <c r="A37" s="1" t="s">
+        <v>276</v>
+      </c>
+      <c r="B37" s="1" t="s">
+        <v>277</v>
+      </c>
+      <c r="C37" s="1" t="s">
+        <v>278</v>
+      </c>
+      <c r="D37" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="E37" s="1" t="s">
+        <v>279</v>
+      </c>
+      <c r="F37" s="1" t="s">
+        <v>280</v>
+      </c>
+      <c r="G37" s="1">
+        <v>2025</v>
+      </c>
+      <c r="K37" s="2" t="s">
+        <v>282</v>
+      </c>
+      <c r="L37" s="2" t="s">
+        <v>283</v>
+      </c>
+      <c r="O37" s="1" t="s">
+        <v>281</v>
+      </c>
+      <c r="R37" s="1" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="38" spans="1:18" ht="60" x14ac:dyDescent="0.25">
+      <c r="A38" s="1" t="s">
+        <v>284</v>
+      </c>
+      <c r="B38" s="1" t="s">
+        <v>285</v>
+      </c>
+      <c r="C38" s="1" t="s">
+        <v>286</v>
+      </c>
+      <c r="D38" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="E38" s="1" t="s">
+        <v>287</v>
+      </c>
+      <c r="F38" s="1" t="s">
+        <v>288</v>
+      </c>
+      <c r="G38" s="1">
+        <v>2024</v>
+      </c>
+      <c r="H38" s="1">
+        <v>64</v>
+      </c>
+      <c r="I38" s="1">
+        <v>1</v>
+      </c>
+      <c r="J38" s="3" t="s">
+        <v>291</v>
+      </c>
+      <c r="K38" s="2" t="s">
+        <v>289</v>
+      </c>
+      <c r="L38" s="2" t="s">
+        <v>290</v>
+      </c>
+      <c r="N38" s="2" t="s">
+        <v>292</v>
+      </c>
+      <c r="O38" s="1" t="s">
+        <v>293</v>
+      </c>
+      <c r="P38" s="1">
+        <v>6</v>
+      </c>
+      <c r="R38" s="1" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="39" spans="1:18" ht="30" x14ac:dyDescent="0.25">
+      <c r="A39" s="1" t="s">
+        <v>294</v>
+      </c>
+      <c r="B39" s="1" t="s">
+        <v>295</v>
+      </c>
+      <c r="C39" s="1" t="s">
+        <v>269</v>
+      </c>
+      <c r="D39" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="E39" s="1" t="s">
+        <v>296</v>
+      </c>
+      <c r="F39" s="1">
+        <v>10255834</v>
+      </c>
+      <c r="G39" s="1">
+        <v>2024</v>
+      </c>
+      <c r="H39" s="1">
+        <v>2024</v>
+      </c>
+      <c r="I39" s="1">
+        <v>128</v>
+      </c>
+      <c r="J39" s="3" t="s">
+        <v>297</v>
+      </c>
+      <c r="K39" s="2" t="s">
+        <v>298</v>
+      </c>
+      <c r="L39" s="2" t="s">
+        <v>299</v>
+      </c>
+      <c r="N39" s="2" t="s">
+        <v>300</v>
+      </c>
+      <c r="O39" s="1" t="s">
+        <v>301</v>
+      </c>
+      <c r="P39" s="1">
+        <v>2</v>
+      </c>
+      <c r="R39" s="1" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="40" spans="1:18" ht="45" x14ac:dyDescent="0.25">
+      <c r="A40" s="1" t="s">
+        <v>302</v>
+      </c>
+      <c r="B40" s="1" t="s">
+        <v>303</v>
+      </c>
+      <c r="C40" s="1" t="s">
+        <v>269</v>
+      </c>
+      <c r="D40" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="E40" s="1" t="s">
+        <v>81</v>
+      </c>
+      <c r="F40" s="1" t="s">
+        <v>304</v>
+      </c>
+      <c r="G40" s="1">
+        <v>2024</v>
+      </c>
+      <c r="H40" s="1">
+        <v>3029</v>
+      </c>
+      <c r="I40" s="1">
+        <v>1</v>
+      </c>
+      <c r="K40" s="2" t="s">
+        <v>305</v>
+      </c>
+      <c r="L40" s="2" t="s">
+        <v>306</v>
+      </c>
+      <c r="N40" s="2" t="s">
+        <v>84</v>
+      </c>
+      <c r="O40" s="1" t="s">
+        <v>307</v>
+      </c>
+      <c r="R40" s="1" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="41" spans="1:18" ht="45" x14ac:dyDescent="0.25">
+      <c r="A41" s="1" t="s">
+        <v>308</v>
+      </c>
+      <c r="B41" s="1" t="s">
+        <v>309</v>
+      </c>
+      <c r="C41" s="1" t="s">
+        <v>310</v>
+      </c>
+      <c r="D41" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="E41" s="1" t="s">
+        <v>81</v>
+      </c>
+      <c r="F41" s="1" t="s">
+        <v>304</v>
+      </c>
+      <c r="G41" s="1">
+        <v>2024</v>
+      </c>
+      <c r="H41" s="1">
+        <v>3029</v>
+      </c>
+      <c r="I41" s="1">
+        <v>1</v>
+      </c>
+      <c r="K41" s="2" t="s">
+        <v>311</v>
+      </c>
+      <c r="L41" s="2" t="s">
+        <v>312</v>
+      </c>
+      <c r="N41" s="2" t="s">
+        <v>84</v>
+      </c>
+      <c r="O41" s="1" t="s">
+        <v>313</v>
+      </c>
+      <c r="R41" s="1" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="42" spans="1:18" ht="30" x14ac:dyDescent="0.25">
+      <c r="A42" s="1" t="s">
+        <v>314</v>
+      </c>
+      <c r="B42" s="1" t="s">
+        <v>315</v>
+      </c>
+      <c r="C42" s="1" t="s">
+        <v>315</v>
+      </c>
+      <c r="D42" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="E42" s="1" t="s">
+        <v>81</v>
+      </c>
+      <c r="F42" s="1" t="s">
+        <v>304</v>
+      </c>
+      <c r="G42" s="1">
+        <v>2024</v>
+      </c>
+      <c r="H42" s="1">
+        <v>3029</v>
+      </c>
+      <c r="I42" s="1">
+        <v>1</v>
+      </c>
+      <c r="K42" s="2" t="s">
+        <v>316</v>
+      </c>
+      <c r="L42" s="2" t="s">
+        <v>317</v>
+      </c>
+      <c r="N42" s="2" t="s">
+        <v>84</v>
+      </c>
+      <c r="O42" s="1" t="s">
+        <v>318</v>
+      </c>
+      <c r="R42" s="1" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="43" spans="1:18" ht="45" x14ac:dyDescent="0.25">
+      <c r="A43" s="1" t="s">
+        <v>319</v>
+      </c>
+      <c r="B43" s="1" t="s">
+        <v>320</v>
+      </c>
+      <c r="C43" s="1" t="s">
+        <v>321</v>
+      </c>
+      <c r="D43" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="E43" s="1" t="s">
+        <v>81</v>
+      </c>
+      <c r="F43" s="1" t="s">
+        <v>304</v>
+      </c>
+      <c r="G43" s="1">
+        <v>2024</v>
+      </c>
+      <c r="H43" s="1">
+        <v>3029</v>
+      </c>
+      <c r="I43" s="1">
+        <v>1</v>
+      </c>
+      <c r="K43" s="2" t="s">
+        <v>322</v>
+      </c>
+      <c r="L43" s="2" t="s">
+        <v>323</v>
+      </c>
+      <c r="N43" s="2" t="s">
+        <v>84</v>
+      </c>
+      <c r="O43" s="1" t="s">
+        <v>324</v>
+      </c>
+      <c r="R43" s="1" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="44" spans="1:18" ht="45" x14ac:dyDescent="0.25">
+      <c r="A44" s="1" t="s">
+        <v>325</v>
+      </c>
+      <c r="B44" s="1" t="s">
+        <v>326</v>
+      </c>
+      <c r="C44" s="1" t="s">
+        <v>327</v>
+      </c>
+      <c r="D44" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="E44" s="1" t="s">
+        <v>81</v>
+      </c>
+      <c r="F44" s="1" t="s">
+        <v>304</v>
+      </c>
+      <c r="G44" s="1">
+        <v>2023</v>
+      </c>
+      <c r="H44" s="1">
+        <v>2714</v>
+      </c>
+      <c r="I44" s="1">
+        <v>1</v>
+      </c>
+      <c r="K44" s="2" t="s">
+        <v>328</v>
+      </c>
+      <c r="L44" s="2" t="s">
+        <v>329</v>
+      </c>
+      <c r="N44" s="2" t="s">
+        <v>84</v>
+      </c>
+      <c r="O44" s="1" t="s">
+        <v>330</v>
+      </c>
+      <c r="P44" s="1">
+        <v>1</v>
+      </c>
+      <c r="R44" s="1" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="45" spans="1:18" ht="45" x14ac:dyDescent="0.25">
+      <c r="A45" s="1" t="s">
+        <v>331</v>
+      </c>
+      <c r="B45" s="1" t="s">
+        <v>332</v>
+      </c>
+      <c r="C45" s="1" t="s">
+        <v>332</v>
+      </c>
+      <c r="D45" s="1" t="s">
+        <v>261</v>
+      </c>
+      <c r="E45" s="1" t="s">
+        <v>333</v>
+      </c>
+      <c r="G45" s="1">
+        <v>2023</v>
+      </c>
+      <c r="K45" s="2" t="s">
+        <v>335</v>
+      </c>
+      <c r="L45" s="2" t="s">
+        <v>336</v>
+      </c>
+      <c r="O45" s="1" t="s">
+        <v>334</v>
+      </c>
+      <c r="P45" s="1">
+        <v>3</v>
+      </c>
+      <c r="R45" s="1" t="s">
         <v>66</v>
       </c>
     </row>
@@ -2390,6 +3493,53 @@
     <hyperlink ref="K28" r:id="rId78" xr:uid="{0396BDDE-16AD-4041-84C2-8820BE0C6DCE}"/>
     <hyperlink ref="L28" r:id="rId79" xr:uid="{1D478E71-9AFF-411C-9459-A55629F95013}"/>
     <hyperlink ref="N28" r:id="rId80" xr:uid="{A71A81B6-B648-49BD-B645-277DC4948106}"/>
+    <hyperlink ref="K29" r:id="rId81" xr:uid="{B9884F0D-AB43-476D-BEBD-EFD215BD02E6}"/>
+    <hyperlink ref="L29" r:id="rId82" xr:uid="{B9732D97-D75E-4882-BE19-B1CD3CC818A3}"/>
+    <hyperlink ref="K30" r:id="rId83" xr:uid="{D9F47DC1-63C6-4A88-BB19-DD81AFE4182E}"/>
+    <hyperlink ref="L30" r:id="rId84" xr:uid="{10B42B6E-1F52-42D0-B6F1-39C0C85655C4}"/>
+    <hyperlink ref="N30" r:id="rId85" xr:uid="{897651E5-57C7-4807-9A8A-46B742A217F9}"/>
+    <hyperlink ref="K31" r:id="rId86" xr:uid="{BD93979B-0C98-4B76-AED9-630C6652726B}"/>
+    <hyperlink ref="L31" r:id="rId87" xr:uid="{050BB1FA-6109-4CE4-9A13-C54E96640465}"/>
+    <hyperlink ref="N31" r:id="rId88" xr:uid="{236A400D-6BA6-48FE-B95B-20EFF1559265}"/>
+    <hyperlink ref="K32" r:id="rId89" xr:uid="{50241FDE-3279-4748-B0D8-29914EE9E4EF}"/>
+    <hyperlink ref="L32" r:id="rId90" xr:uid="{59FD887B-DF46-43A4-A3EC-D877F4DF917A}"/>
+    <hyperlink ref="N32" r:id="rId91" xr:uid="{5483A64D-43A5-4F25-BE1F-680C3EAD48FC}"/>
+    <hyperlink ref="K33" r:id="rId92" xr:uid="{F8DADE4D-5CF6-40D5-9F56-3EE771E531BB}"/>
+    <hyperlink ref="L33" r:id="rId93" xr:uid="{5ACC2158-552F-4F79-8809-41E52E00A844}"/>
+    <hyperlink ref="K34" r:id="rId94" xr:uid="{59330331-3973-4F4B-BFD5-4B6664A93CE7}"/>
+    <hyperlink ref="L34" r:id="rId95" xr:uid="{A5461029-641F-4B09-A46D-51B443F42618}"/>
+    <hyperlink ref="N34" r:id="rId96" xr:uid="{AFE87BEA-BC5E-4108-B6D7-BDC8DD05FAD2}"/>
+    <hyperlink ref="K35" r:id="rId97" xr:uid="{56044E5E-2060-4A89-A0FB-D62E1C15FDBF}"/>
+    <hyperlink ref="L35" r:id="rId98" xr:uid="{B1CFBCAC-F35C-4A75-8B90-3C68507B0E21}"/>
+    <hyperlink ref="O35" r:id="rId99" xr:uid="{B3CA40F1-3366-4226-A140-5273DE899919}"/>
+    <hyperlink ref="K36" r:id="rId100" xr:uid="{456402DA-6C56-47F9-A589-D2086BBF643B}"/>
+    <hyperlink ref="L36" r:id="rId101" xr:uid="{15E14F3A-54E6-4225-A8F0-75DE287FA132}"/>
+    <hyperlink ref="N36" r:id="rId102" xr:uid="{CC92E16F-FCA0-4E85-8227-1F2F61DE29E0}"/>
+    <hyperlink ref="K37" r:id="rId103" xr:uid="{1E408E0C-702D-4610-B3F0-2967014961B4}"/>
+    <hyperlink ref="L37" r:id="rId104" xr:uid="{3C62213A-BB44-4A98-8B59-41DC48727BF7}"/>
+    <hyperlink ref="K38" r:id="rId105" xr:uid="{7F2B3ABC-885E-46BA-99A8-A7D14F7A16D9}"/>
+    <hyperlink ref="L38" r:id="rId106" xr:uid="{EE94E29B-4F20-4CBE-879A-9E04EB389218}"/>
+    <hyperlink ref="N38" r:id="rId107" xr:uid="{73FB8AC2-7910-46EF-8FBC-82C28BCD6A2A}"/>
+    <hyperlink ref="K39" r:id="rId108" xr:uid="{824053F7-B23C-4C56-B83D-21291B63F95E}"/>
+    <hyperlink ref="L39" r:id="rId109" xr:uid="{3E455ED4-CA9B-455A-98D5-2D64B8279FC6}"/>
+    <hyperlink ref="N39" r:id="rId110" xr:uid="{B171A4F6-0984-4B4D-98F2-F7CC499CC0B1}"/>
+    <hyperlink ref="K40" r:id="rId111" xr:uid="{44B7E379-C01A-46EF-B49E-773F31BDBEBE}"/>
+    <hyperlink ref="L40" r:id="rId112" xr:uid="{6AD35221-59B2-4EEB-AE92-B8B43A761205}"/>
+    <hyperlink ref="N40" r:id="rId113" xr:uid="{8BB120AD-35F9-461A-AB67-EF52133D7528}"/>
+    <hyperlink ref="K41" r:id="rId114" xr:uid="{6D4AC69D-02B7-4385-9B30-CE2D5640D1F7}"/>
+    <hyperlink ref="L41" r:id="rId115" xr:uid="{46EBF7D6-4C70-499E-B939-EA42806DA895}"/>
+    <hyperlink ref="N41" r:id="rId116" xr:uid="{65321ACE-53E1-4DE1-8493-24961F0CE700}"/>
+    <hyperlink ref="K42" r:id="rId117" xr:uid="{D3BF350F-D5B6-4B6B-9C13-4324BC656DF9}"/>
+    <hyperlink ref="L42" r:id="rId118" xr:uid="{4B2AFE00-E17B-4EA2-A25A-B56567079345}"/>
+    <hyperlink ref="N42" r:id="rId119" xr:uid="{5F90EE86-70D6-4748-861F-5839D89B8DC6}"/>
+    <hyperlink ref="K43" r:id="rId120" xr:uid="{5903BB32-02B5-43F0-867A-AF0CE561A88F}"/>
+    <hyperlink ref="L43" r:id="rId121" xr:uid="{3C8905A9-C97E-46BE-A42C-5861899962F3}"/>
+    <hyperlink ref="N43" r:id="rId122" xr:uid="{11550CBA-0C9F-4527-A0AF-E1F5B674A80A}"/>
+    <hyperlink ref="K44" r:id="rId123" xr:uid="{1EF988B9-248D-4B61-86BA-46F34FDCE678}"/>
+    <hyperlink ref="L44" r:id="rId124" xr:uid="{CD008A4E-C12B-4FE2-80D9-9D00ECCC098B}"/>
+    <hyperlink ref="N44" r:id="rId125" xr:uid="{2601B3E4-C3D3-472A-BCA1-F16A4684E5CB}"/>
+    <hyperlink ref="K45" r:id="rId126" xr:uid="{62D9F48F-400F-418C-9733-C56FE95796F5}"/>
+    <hyperlink ref="L45" r:id="rId127" xr:uid="{A46EDA6E-59E3-4B4B-ABA8-BFE2A25AF1DF}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
